--- a/output/pdf_financials_xlsx/BRAU.xlsx
+++ b/output/pdf_financials_xlsx/BRAU.xlsx
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.676772</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1.365964</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>1.854107</v>
@@ -1390,10 +1390,10 @@
         <v>-0.591672</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.084129</v>
+        <v>0.044125</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.12903</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1401,19 +1401,19 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="17">
@@ -1429,7 +1429,7 @@
         <v>-1.365964</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.33516</v>
+        <v>-1.481744</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.838386</v>
+        <v>-1.838386</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.257142</v>
+        <v>-1.257142</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.573292</v>
+        <v>-0.573292</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.854107</v>
@@ -1706,10 +1706,10 @@
         <v>-0.295836</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.020002</v>
+        <v>-1.020002</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.564515</v>
+        <v>-0.564515</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1717,19 +1717,19 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="21">
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.838386</v>
+        <v>-1.838386</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.257142</v>
+        <v>-1.257142</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.573292</v>
+        <v>-0.573292</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1.854107</v>
@@ -1904,10 +1904,10 @@
         <v>-0.295836</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.020002</v>
+        <v>-1.020002</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.564515</v>
+        <v>-0.564515</v>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="24">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>91.91930000000001</v>
+        <v>-91.91930000000001</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>25.522975</v>
+        <v>-25.522975</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>23.176338</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>51.0001</v>
+        <v>-51.0001</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.676772</v>
+        <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.365964</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.854107</v>
@@ -2210,10 +2210,10 @@
         <v>-0.591672</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.084129</v>
+        <v>0.044125</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.12903</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="28">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.676772</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.365964</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.854107</v>
@@ -2342,10 +2342,10 @@
         <v>-0.591672</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.084129</v>
+        <v>0.044125</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.12903</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2353,19 +2353,19 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="30">
@@ -2466,14 +2466,16 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>50</v>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="3" t="n">
         <v>100</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>36.89352877202098</v>
+        <v>163.106471227979</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2491,7 +2493,7 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
@@ -2500,10 +2502,12 @@
         <v>-50</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>51.05859570112982</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>50</v>
+        <v>2411.619263456091</v>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -2511,19 +2515,19 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -7589,7 +7593,7 @@
         <v>-1.854107</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.295835</v>
+        <v>-0.295835</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-1.020002</v>
@@ -7823,10 +7827,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.021849</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.026439</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -7847,19 +7851,19 @@
         </is>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.002729</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.052375</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.045341</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002121</v>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
@@ -8021,10 +8025,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.123393</v>
+        <v>0.145242</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.09134100000000001</v>
+        <v>-0.11778</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.196526</v>
@@ -8045,19 +8049,19 @@
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.016093</v>
+        <v>-0.013364</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-0.020156</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.032529</v>
+        <v>-0.019846</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.006119</v>
+        <v>0.039222</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.023485</v>
+        <v>-0.025606</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -10567,7 +10571,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -16480,7 +16488,11 @@
           <t>Prepaids and Deposits</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -38010,7 +38022,11 @@
           <t>Decrease (increase) in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -41113,7 +41129,11 @@
           <t>Decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -42249,13 +42269,13 @@
         </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>0.295836</v>
+        <v>-0.295836</v>
       </c>
       <c r="M321" s="5" t="n">
-        <v>0.295835</v>
+        <v>-0.295835</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>0.295835</v>
+        <v>-0.295835</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -43117,7 +43137,11 @@
           <t>(Increase) in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -53615,7 +53639,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E434" s="5" t="n">
         <v>0.021849</v>
       </c>
@@ -56188,19 +56216,19 @@
         </is>
       </c>
       <c r="Q459" s="5" t="n">
-        <v>0.913484</v>
+        <v>-0.913484</v>
       </c>
       <c r="R459" s="5" t="n">
-        <v>12.724632</v>
+        <v>-12.724632</v>
       </c>
       <c r="S459" s="5" t="n">
-        <v>3.68077</v>
+        <v>-3.68077</v>
       </c>
       <c r="T459" s="5" t="n">
-        <v>4.806136</v>
+        <v>-4.806136</v>
       </c>
       <c r="U459" s="5" t="n">
-        <v>2.324063</v>
+        <v>-2.324063</v>
       </c>
     </row>
     <row r="460">
@@ -59227,10 +59255,10 @@
         </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>1.020919</v>
+        <v>-1.020919</v>
       </c>
       <c r="L490" s="5" t="n">
-        <v>1.854107</v>
+        <v>-1.854107</v>
       </c>
       <c r="M490" t="inlineStr">
         <is>
@@ -59238,10 +59266,10 @@
         </is>
       </c>
       <c r="N490" s="5" t="n">
-        <v>1.020002</v>
+        <v>-1.020002</v>
       </c>
       <c r="O490" s="5" t="n">
-        <v>0.564515</v>
+        <v>-0.564515</v>
       </c>
       <c r="P490" t="inlineStr">
         <is>
@@ -59440,10 +59468,10 @@
         </is>
       </c>
       <c r="N492" s="5" t="n">
-        <v>1.013283</v>
+        <v>-1.013283</v>
       </c>
       <c r="O492" s="5" t="n">
-        <v>0.564515</v>
+        <v>-0.564515</v>
       </c>
       <c r="P492" t="inlineStr">
         <is>
@@ -63235,10 +63263,10 @@
         </is>
       </c>
       <c r="K530" s="5" t="n">
-        <v>0.941866</v>
+        <v>-0.941866</v>
       </c>
       <c r="L530" s="5" t="n">
-        <v>0.34156</v>
+        <v>-0.34156</v>
       </c>
       <c r="M530" t="inlineStr">
         <is>
@@ -66226,10 +66254,10 @@
         </is>
       </c>
       <c r="F560" s="5" t="n">
-        <v>1.257142</v>
+        <v>-1.257142</v>
       </c>
       <c r="G560" s="5" t="n">
-        <v>0.573292</v>
+        <v>-0.573292</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
@@ -68653,10 +68681,10 @@
         </is>
       </c>
       <c r="E584" s="5" t="n">
-        <v>1.838386</v>
+        <v>-1.838386</v>
       </c>
       <c r="F584" s="5" t="n">
-        <v>1.257142</v>
+        <v>-1.257142</v>
       </c>
       <c r="G584" t="inlineStr">
         <is>
@@ -69156,10 +69184,10 @@
         </is>
       </c>
       <c r="E589" s="5" t="n">
-        <v>1.838386</v>
+        <v>-1.838386</v>
       </c>
       <c r="F589" s="5" t="n">
-        <v>1.257142</v>
+        <v>-1.257142</v>
       </c>
       <c r="G589" t="inlineStr">
         <is>
@@ -69463,10 +69491,10 @@
         </is>
       </c>
       <c r="E592" s="5" t="n">
-        <v>1.853936</v>
+        <v>-1.853936</v>
       </c>
       <c r="F592" s="5" t="n">
-        <v>1.122062</v>
+        <v>-1.122062</v>
       </c>
       <c r="G592" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BRAU.xlsx
+++ b/output/pdf_financials_xlsx/BRAU.xlsx
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.04362</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005155</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014486</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-8.8e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0</v>
+        <v>0.04362</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.365964</v>
+        <v>1.371119</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.908452</v>
+        <v>0.922938</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.020919</v>
+        <v>-1.020831</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.854107</v>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0</v>
+        <v>0.04362</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.365964</v>
+        <v>1.371119</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.908452</v>
+        <v>0.922938</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.020919</v>
+        <v>-1.020831</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.854107</v>
@@ -2639,10 +2639,10 @@
         <v>0.771652</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.052369</v>
+        <v>0.317369</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.302226</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2660,19 +2660,19 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.198456</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.11755</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.951043</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.372471</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.789245</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2791,10 +2791,10 @@
         <v>0.771652</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.421467</v>
+        <v>0.686467</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.401806</v>
+        <v>0.704032</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.06490600000000001</v>
+        <v>0.263362</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.062081</v>
+        <v>0.179631</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.734813</v>
+        <v>1.685856</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.246531</v>
+        <v>1.619002</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.302784</v>
+        <v>1.092029</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>0.465762</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.312888</v>
+        <v>1.047888</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.199205</v>
+        <v>0.000749</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.118299</v>
+        <v>0.000749</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.004167</v>
+        <v>0.053124</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.380252</v>
+        <v>0.007781</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.799149</v>
+        <v>0.009904</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -9268,10 +9268,10 @@
         <v>0</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009707</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009707</v>
       </c>
     </row>
     <row r="125">
@@ -9334,10 +9334,10 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009707</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009707</v>
       </c>
     </row>
     <row r="126">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20783,7 +20783,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -57645,7 +57649,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -62615,7 +62619,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -65641,7 +65645,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -68269,7 +68273,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E580" s="5" t="n">
